--- a/sports_forms/002_psa_form--sports_forms.xlsx
+++ b/sports_forms/002_psa_form--sports_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,8 +442,8 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,23 +515,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>kids_count</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kids_list</t>
+          <t>How many children do you have?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +548,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>first_kid_name</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What is the name of your first child?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please enter the name of your first child</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,13 +575,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>What is your first child's date of birth?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>mm/dd/yyyy</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,20 +602,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>assessment_level</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What is your first child's assessment level?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Select level for your first child</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,13 +629,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>medical_conditions</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Does your first child have any medical conditions?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Select all conditions</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,13 +656,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>second_kid_name</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>What is your second child's name?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please enter the name of your second child</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -663,13 +683,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>What is your second child's date of birth?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>mm/dd/yyyy</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -686,20 +710,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>assessment_level</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>What is your second child's assessment level?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Select level for your second child</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,13 +737,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>medical_conditions</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Does your second child have any medical conditions?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Select all conditions</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -732,13 +764,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>third_kid_name</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>What is your third child's name?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please enter the name of your third child</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -755,13 +791,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>What is your third child's date of birth?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>mm/dd/yyyy</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -778,20 +818,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>assessment_level</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>What is your third child's assessment level?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Select level for your third child</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -801,13 +845,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>medical_conditions</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Does your third child have any medical conditions?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Select all conditions</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -824,10 +872,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>fourth_kid_name</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>What is your fourth child's name?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Please enter the name of your fourth child</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -847,10 +899,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>What is your fourth child's date of birth?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>mm/dd/yyyy</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -870,10 +926,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>assessment_level</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>What is your fourth child's assessment level?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Select level for your fourth child</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -883,7 +943,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -893,10 +953,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>medical_conditions</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Does your fourth child have any medical conditions?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Select all conditions</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -916,10 +980,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>fifth_kid_name</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>What is your fifth child's name?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Please enter the name of your fifth child</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
@@ -939,10 +1007,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>What is your fifth child's date of birth?</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>mm/dd/yyyy</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>no</t>
@@ -962,10 +1034,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>assessment_level</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>What is your fifth child's assessment level?</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Select level for your fifth child</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>no</t>
@@ -975,7 +1051,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -985,10 +1061,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>medical_conditions</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Does your fifth child have any medical conditions?</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Select all conditions</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>no</t>
@@ -998,7 +1078,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1008,13 +1088,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>media_declaration</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>Do you consent to the collection and use of your child's information for the purpose of this assessment?</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1031,10 +1115,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>terms_and_conditions</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Terms and Conditions</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>no</t>
@@ -1054,10 +1142,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>confirm</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>Confirmation</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>no</t>
@@ -1075,12 +1167,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1103,34 +1195,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>kids_choices</t>
+          <t>first_kid_level_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>level_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Level 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>kids_choices</t>
+          <t>first_kid_level_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>level_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Level 2</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1234,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>level_1</t>
+          <t>level_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Level 1</t>
+          <t>Level 3</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1251,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>level_2</t>
+          <t>level_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 4</t>
         </is>
       </c>
     </row>
@@ -1176,80 +1268,80 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>level_3</t>
+          <t>level_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>first_kid_level_choices</t>
+          <t>first_kid_medical_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>level_4</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Level 4</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>first_kid_level_choices</t>
+          <t>first_kid_medical_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>level_5</t>
+          <t>condition_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Level 5</t>
+          <t>Condition 1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>second_kid_level_choices</t>
+          <t>first_kid_medical_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>level_1</t>
+          <t>condition_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Level 1</t>
+          <t>Condition 2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>second_kid_level_choices</t>
+          <t>first_kid_medical_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>level_2</t>
+          <t>condition_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Condition 3</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1353,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>level_3</t>
+          <t>level_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 1</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1370,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>level_4</t>
+          <t>level_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Level 4</t>
+          <t>Level 2</t>
         </is>
       </c>
     </row>
@@ -1295,316 +1387,673 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>level_5</t>
+          <t>level_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Level 5</t>
+          <t>Level 3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>third_kid_level_choices</t>
+          <t>second_kid_level_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>level_1</t>
+          <t>level_4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Level 1</t>
+          <t>Level 4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>third_kid_level_choices</t>
+          <t>second_kid_level_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>level_2</t>
+          <t>level_5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>third_kid_level_choices</t>
+          <t>second_kid_medical_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>level_3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>third_kid_level_choices</t>
+          <t>second_kid_medical_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>level_4</t>
+          <t>condition_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Level 4</t>
+          <t>Condition 1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>third_kid_level_choices</t>
+          <t>second_kid_medical_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>level_5</t>
+          <t>condition_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Level 5</t>
+          <t>Condition 2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fourth_kid_level_choices</t>
+          <t>second_kid_medical_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>level_1</t>
+          <t>condition_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Level 1</t>
+          <t>Condition 3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>fourth_kid_level_choices</t>
+          <t>third_kid_level_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>level_2</t>
+          <t>level_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fourth_kid_level_choices</t>
+          <t>third_kid_level_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>level_3</t>
+          <t>level_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fourth_kid_level_choices</t>
+          <t>third_kid_level_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>level_4</t>
+          <t>level_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Level 4</t>
+          <t>Level 3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>fourth_kid_level_choices</t>
+          <t>third_kid_level_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>level_5</t>
+          <t>level_4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Level 5</t>
+          <t>Level 4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>fifth_kid_level_choices</t>
+          <t>third_kid_level_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>level_1</t>
+          <t>level_5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Level 1</t>
+          <t>Level 5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>fifth_kid_level_choices</t>
+          <t>third_kid_medical_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>level_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>fifth_kid_level_choices</t>
+          <t>third_kid_medical_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>level_3</t>
+          <t>condition_1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Condition 1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>fifth_kid_level_choices</t>
+          <t>third_kid_medical_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>level_4</t>
+          <t>condition_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Level 4</t>
+          <t>Condition 2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>fifth_kid_level_choices</t>
+          <t>third_kid_medical_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>level_5</t>
+          <t>condition_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Level 5</t>
+          <t>Condition 3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>agreement_choices</t>
+          <t>fourth_kid_level_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>level_1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Level 1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>agreement_choices</t>
+          <t>fourth_kid_level_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>level_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Level 2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>fourth_kid_level_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>level_3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Level 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>fourth_kid_level_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>level_4</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Level 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>fourth_kid_level_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>level_5</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>fourth_kid_medical_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>fourth_kid_medical_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>condition_1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Condition 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>fourth_kid_medical_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>condition_2</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Condition 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>fourth_kid_medical_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>condition_3</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Condition 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>fifth_kid_level_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>level_1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>fifth_kid_level_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>level_2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>fifth_kid_level_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>level_3</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Level 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>fifth_kid_level_choices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>level_4</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Level 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>fifth_kid_level_choices</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>level_5</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>fifth_kid_medical_choices</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>fifth_kid_medical_choices</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>condition_1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Condition 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>fifth_kid_medical_choices</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>condition_2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Condition 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>fifth_kid_medical_choices</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>condition_3</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Condition 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>media_declaration_choices</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>media_declaration_choices</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>media_declaration_choices</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>decline</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Decline</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>agreement_choices</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>agreement_choices</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>agreement_choices</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
         <is>
           <t>decline</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Decline</t>
         </is>
